--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -1,181 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengbotao/fruit/src/excel/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85289A1-EB91-1240-BC08-54DB55C46378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="28600" yWindow="-21720" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="45">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>difficulty</t>
-  </si>
-  <si>
-    <t>colorKindCount</t>
-  </si>
-  <si>
-    <t>fruitCountRange</t>
-  </si>
-  <si>
-    <t>radiusRange</t>
-  </si>
-  <si>
-    <t>speedRange</t>
-  </si>
-  <si>
-    <t>seed</t>
-  </si>
-  <si>
-    <t>简单-01</t>
-  </si>
-  <si>
-    <t>easy</t>
-  </si>
-  <si>
-    <t>14,26</t>
-  </si>
-  <si>
-    <t>0.22,0.38</t>
-  </si>
-  <si>
-    <t>0.00,0.20</t>
-  </si>
-  <si>
-    <t>简单-02</t>
-  </si>
-  <si>
-    <t>简单-03</t>
-  </si>
-  <si>
-    <t>简单-04</t>
-  </si>
-  <si>
-    <t>中等-05</t>
-  </si>
-  <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>22,34</t>
-  </si>
-  <si>
-    <t>0.20,0.40</t>
-  </si>
-  <si>
-    <t>0.04,0.28</t>
-  </si>
-  <si>
-    <t>简单-06</t>
-  </si>
-  <si>
-    <t>简单-07</t>
-  </si>
-  <si>
-    <t>简单-08</t>
-  </si>
-  <si>
-    <t>简单-09</t>
-  </si>
-  <si>
-    <t>困难-10</t>
-  </si>
-  <si>
-    <t>hard</t>
-  </si>
-  <si>
-    <t>28,40</t>
-  </si>
-  <si>
-    <t>0.20,0.42</t>
-  </si>
-  <si>
-    <t>0.06,0.32</t>
-  </si>
-  <si>
-    <t>简单-11</t>
-  </si>
-  <si>
-    <t>18,32</t>
-  </si>
-  <si>
-    <t>0.02,0.24</t>
-  </si>
-  <si>
-    <t>简单-12</t>
-  </si>
-  <si>
-    <t>简单-13</t>
-  </si>
-  <si>
-    <t>简单-14</t>
-  </si>
-  <si>
-    <t>中等-15</t>
-  </si>
-  <si>
-    <t>26,36</t>
-  </si>
-  <si>
-    <t>简单-16</t>
-  </si>
-  <si>
-    <t>简单-17</t>
-  </si>
-  <si>
-    <t>简单-18</t>
-  </si>
-  <si>
-    <t>简单-19</t>
-  </si>
-  <si>
-    <t>困难-20</t>
-  </si>
-  <si>
-    <t>8,12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12,18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -200,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -539,565 +396,621 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.5" customWidth="1"/>
-    <col min="7" max="7" width="15.5" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I21"/>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>difficulty</v>
+      </c>
+      <c r="D1" t="str">
+        <v>colorKindCount</v>
+      </c>
+      <c r="E1" t="str">
+        <v>fruitCountRange</v>
+      </c>
+      <c r="F1" t="str">
+        <v>radiusRange</v>
+      </c>
+      <c r="G1" t="str">
+        <v>speedRange</v>
+      </c>
+      <c r="H1" t="str">
+        <v>seed</v>
+      </c>
+      <c r="I1" t="str">
+        <v>homeBubbleColorId</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
+      <c r="B2" t="str">
+        <v>简单-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>easy</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
+      <c r="E2" t="str">
+        <v>8,12</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G2" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H2">
         <v>41113</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3" t="str">
+        <v>简单-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>easy</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
+      <c r="E3" t="str">
+        <v>12,18</v>
+      </c>
+      <c r="F3" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G3" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H3">
         <v>41226</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
+      <c r="B4" t="str">
+        <v>简单-03</v>
+      </c>
+      <c r="C4" t="str">
+        <v>easy</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
+      <c r="E4" t="str">
+        <v>14,26</v>
+      </c>
+      <c r="F4" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G4" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H4">
         <v>41339</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
+      <c r="B5" t="str">
+        <v>简单-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>easy</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
+      <c r="E5" t="str">
+        <v>14,26</v>
+      </c>
+      <c r="F5" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G5" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H5">
         <v>41452</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+      <c r="B6" t="str">
+        <v>中等-05</v>
+      </c>
+      <c r="C6" t="str">
+        <v>medium</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
+      <c r="E6" t="str">
+        <v>22,34</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0.20,0.40</v>
+      </c>
+      <c r="G6" t="str">
+        <v>0.04,0.28</v>
       </c>
       <c r="H6">
         <v>41565</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
+      <c r="B7" t="str">
+        <v>简单-06</v>
+      </c>
+      <c r="C7" t="str">
+        <v>easy</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
+      <c r="E7" t="str">
+        <v>14,26</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G7" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H7">
         <v>41678</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
+      <c r="B8" t="str">
+        <v>简单-07</v>
+      </c>
+      <c r="C8" t="str">
+        <v>easy</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>12</v>
+      <c r="E8" t="str">
+        <v>14,26</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G8" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H8">
         <v>41791</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
+      <c r="B9" t="str">
+        <v>简单-08</v>
+      </c>
+      <c r="C9" t="str">
+        <v>easy</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>12</v>
+      <c r="E9" t="str">
+        <v>14,26</v>
+      </c>
+      <c r="F9" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G9" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H9">
         <v>41904</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
+      <c r="B10" t="str">
+        <v>简单-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>easy</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
+      <c r="E10" t="str">
+        <v>14,26</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G10" t="str">
+        <v>0.00,0.20</v>
       </c>
       <c r="H10">
         <v>42017</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
+      <c r="B11" t="str">
+        <v>困难-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>hard</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
+      <c r="E11" t="str">
+        <v>28,40</v>
+      </c>
+      <c r="F11" t="str">
+        <v>0.20,0.42</v>
+      </c>
+      <c r="G11" t="str">
+        <v>0.06,0.32</v>
       </c>
       <c r="H11">
         <v>42130</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
+      <c r="B12" t="str">
+        <v>简单-11</v>
+      </c>
+      <c r="C12" t="str">
+        <v>easy</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
+      <c r="E12" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G12" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H12">
         <v>42243</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
+      <c r="B13" t="str">
+        <v>简单-12</v>
+      </c>
+      <c r="C13" t="str">
+        <v>easy</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" t="s">
-        <v>32</v>
+      <c r="E13" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F13" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G13" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H13">
         <v>42356</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
+      <c r="B14" t="str">
+        <v>简单-13</v>
+      </c>
+      <c r="C14" t="str">
+        <v>easy</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
-      <c r="E14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" t="s">
-        <v>32</v>
+      <c r="E14" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G14" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H14">
         <v>42469</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
+      <c r="B15" t="str">
+        <v>简单-14</v>
+      </c>
+      <c r="C15" t="str">
+        <v>easy</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" t="s">
-        <v>32</v>
+      <c r="E15" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H15">
         <v>42582</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
+      <c r="B16" t="str">
+        <v>中等-15</v>
+      </c>
+      <c r="C16" t="str">
+        <v>medium</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
-      <c r="E16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" t="s">
-        <v>20</v>
+      <c r="E16" t="str">
+        <v>26,36</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0.20,0.40</v>
+      </c>
+      <c r="G16" t="str">
+        <v>0.04,0.28</v>
       </c>
       <c r="H16">
         <v>42695</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
+      <c r="B17" t="str">
+        <v>简单-16</v>
+      </c>
+      <c r="C17" t="str">
+        <v>easy</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" t="s">
-        <v>32</v>
+      <c r="E17" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F17" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G17" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H17">
         <v>42808</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
+      <c r="B18" t="str">
+        <v>简单-17</v>
+      </c>
+      <c r="C18" t="str">
+        <v>easy</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" t="s">
-        <v>32</v>
+      <c r="E18" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G18" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H18">
         <v>42921</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
+      <c r="B19" t="str">
+        <v>简单-18</v>
+      </c>
+      <c r="C19" t="str">
+        <v>easy</v>
       </c>
       <c r="D19">
         <v>8</v>
       </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" t="s">
-        <v>32</v>
+      <c r="E19" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F19" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G19" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H19">
         <v>43034</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
+      <c r="B20" t="str">
+        <v>简单-19</v>
+      </c>
+      <c r="C20" t="str">
+        <v>easy</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" t="s">
-        <v>32</v>
+      <c r="E20" t="str">
+        <v>18,32</v>
+      </c>
+      <c r="F20" t="str">
+        <v>0.22,0.38</v>
+      </c>
+      <c r="G20" t="str">
+        <v>0.02,0.24</v>
       </c>
       <c r="H20">
         <v>43147</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
+      <c r="B21" t="str">
+        <v>困难-20</v>
+      </c>
+      <c r="C21" t="str">
+        <v>hard</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" t="s">
-        <v>29</v>
+      <c r="E21" t="str">
+        <v>28,40</v>
+      </c>
+      <c r="F21" t="str">
+        <v>0.20,0.42</v>
+      </c>
+      <c r="G21" t="str">
+        <v>0.06,0.32</v>
       </c>
       <c r="H21">
         <v>43260</v>
       </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -1,58 +1,537 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView windowWidth="30240" windowHeight="13220"/>
+  </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>difficulty</t>
+  </si>
+  <si>
+    <t>colorKindCount</t>
+  </si>
+  <si>
+    <t>fruitCountRange</t>
+  </si>
+  <si>
+    <t>radiusRange</t>
+  </si>
+  <si>
+    <t>speedRange</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>homeBubbleColorId</t>
+  </si>
+  <si>
+    <t>简单-01</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>8,12</t>
+  </si>
+  <si>
+    <t>0.22,0.38</t>
+  </si>
+  <si>
+    <t>0.00,0.20</t>
+  </si>
+  <si>
+    <t>简单-02</t>
+  </si>
+  <si>
+    <t>12,18</t>
+  </si>
+  <si>
+    <t>简单-03</t>
+  </si>
+  <si>
+    <t>14,26</t>
+  </si>
+  <si>
+    <t>简单-04</t>
+  </si>
+  <si>
+    <t>中等-05</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>22,34</t>
+  </si>
+  <si>
+    <t>0.20,0.40</t>
+  </si>
+  <si>
+    <t>0.04,0.28</t>
+  </si>
+  <si>
+    <t>简单-06</t>
+  </si>
+  <si>
+    <t>简单-07</t>
+  </si>
+  <si>
+    <t>简单-08</t>
+  </si>
+  <si>
+    <t>简单-09</t>
+  </si>
+  <si>
+    <t>困难-10</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>28,40</t>
+  </si>
+  <si>
+    <t>0.20,0.42</t>
+  </si>
+  <si>
+    <t>0.06,0.32</t>
+  </si>
+  <si>
+    <t>简单-11</t>
+  </si>
+  <si>
+    <t>18,32</t>
+  </si>
+  <si>
+    <t>0.02,0.24</t>
+  </si>
+  <si>
+    <t>简单-12</t>
+  </si>
+  <si>
+    <t>简单-13</t>
+  </si>
+  <si>
+    <t>简单-14</t>
+  </si>
+  <si>
+    <t>中等-15</t>
+  </si>
+  <si>
+    <t>26,36</t>
+  </si>
+  <si>
+    <t>简单-16</t>
+  </si>
+  <si>
+    <t>简单-17</t>
+  </si>
+  <si>
+    <t>简单-18</t>
+  </si>
+  <si>
+    <t>简单-19</t>
+  </si>
+  <si>
+    <t>困难-20</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -60,18 +539,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -391,64 +1164,74 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="2" max="2" width="17.2589285714286" customWidth="1"/>
+    <col min="4" max="4" width="16.3571428571429" customWidth="1"/>
+    <col min="5" max="5" width="17.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="12.7857142857143" customWidth="1"/>
+    <col min="7" max="7" width="12.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="14.2767857142857" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>difficulty</v>
-      </c>
-      <c r="D1" t="str">
-        <v>colorKindCount</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fruitCountRange</v>
-      </c>
-      <c r="F1" t="str">
-        <v>radiusRange</v>
-      </c>
-      <c r="G1" t="str">
-        <v>speedRange</v>
-      </c>
-      <c r="H1" t="str">
-        <v>seed</v>
-      </c>
-      <c r="I1" t="str">
-        <v>homeBubbleColorId</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>简单-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>easy</v>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="str">
-        <v>8,12</v>
-      </c>
-      <c r="F2" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0.00,0.20</v>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
       <c r="H2">
         <v>41113</v>
@@ -457,27 +1240,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>简单-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>easy</v>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="str">
-        <v>12,18</v>
-      </c>
-      <c r="F3" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G3" t="str">
-        <v>0.00,0.20</v>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
       </c>
       <c r="H3">
         <v>41226</v>
@@ -486,27 +1269,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>简单-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>easy</v>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F4" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G4" t="str">
-        <v>0.00,0.20</v>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
       </c>
       <c r="H4">
         <v>41339</v>
@@ -515,27 +1298,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>简单-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>easy</v>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F5" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G5" t="str">
-        <v>0.00,0.20</v>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
       </c>
       <c r="H5">
         <v>41452</v>
@@ -544,27 +1327,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>中等-05</v>
-      </c>
-      <c r="C6" t="str">
-        <v>medium</v>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" t="str">
-        <v>22,34</v>
-      </c>
-      <c r="F6" t="str">
-        <v>0.20,0.40</v>
-      </c>
-      <c r="G6" t="str">
-        <v>0.04,0.28</v>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
       </c>
       <c r="H6">
         <v>41565</v>
@@ -573,27 +1356,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>简单-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>easy</v>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F7" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G7" t="str">
-        <v>0.00,0.20</v>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
       </c>
       <c r="H7">
         <v>41678</v>
@@ -602,27 +1385,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>简单-07</v>
-      </c>
-      <c r="C8" t="str">
-        <v>easy</v>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
-      <c r="E8" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F8" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G8" t="str">
-        <v>0.00,0.20</v>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
       </c>
       <c r="H8">
         <v>41791</v>
@@ -631,27 +1414,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>简单-08</v>
-      </c>
-      <c r="C9" t="str">
-        <v>easy</v>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F9" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G9" t="str">
-        <v>0.00,0.20</v>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
       </c>
       <c r="H9">
         <v>41904</v>
@@ -660,27 +1443,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>简单-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>easy</v>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F10" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G10" t="str">
-        <v>0.00,0.20</v>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
       </c>
       <c r="H10">
         <v>42017</v>
@@ -689,27 +1472,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>困难-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>hard</v>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="str">
-        <v>28,40</v>
-      </c>
-      <c r="F11" t="str">
-        <v>0.20,0.42</v>
-      </c>
-      <c r="G11" t="str">
-        <v>0.06,0.32</v>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
       </c>
       <c r="H11">
         <v>42130</v>
@@ -718,27 +1501,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>简单-11</v>
-      </c>
-      <c r="C12" t="str">
-        <v>easy</v>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F12" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G12" t="str">
-        <v>0.02,0.24</v>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
       </c>
       <c r="H12">
         <v>42243</v>
@@ -747,27 +1530,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>简单-12</v>
-      </c>
-      <c r="C13" t="str">
-        <v>easy</v>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F13" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G13" t="str">
-        <v>0.02,0.24</v>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
       </c>
       <c r="H13">
         <v>42356</v>
@@ -776,27 +1559,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>简单-13</v>
-      </c>
-      <c r="C14" t="str">
-        <v>easy</v>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
-      <c r="E14" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F14" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G14" t="str">
-        <v>0.02,0.24</v>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
       </c>
       <c r="H14">
         <v>42469</v>
@@ -805,27 +1588,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>简单-14</v>
-      </c>
-      <c r="C15" t="str">
-        <v>easy</v>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F15" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G15" t="str">
-        <v>0.02,0.24</v>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
       </c>
       <c r="H15">
         <v>42582</v>
@@ -834,27 +1617,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>中等-15</v>
-      </c>
-      <c r="C16" t="str">
-        <v>medium</v>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
-      <c r="E16" t="str">
-        <v>26,36</v>
-      </c>
-      <c r="F16" t="str">
-        <v>0.20,0.40</v>
-      </c>
-      <c r="G16" t="str">
-        <v>0.04,0.28</v>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
       </c>
       <c r="H16">
         <v>42695</v>
@@ -863,27 +1646,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>简单-16</v>
-      </c>
-      <c r="C17" t="str">
-        <v>easy</v>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
-      <c r="E17" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F17" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G17" t="str">
-        <v>0.02,0.24</v>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
       </c>
       <c r="H17">
         <v>42808</v>
@@ -892,27 +1675,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>简单-17</v>
-      </c>
-      <c r="C18" t="str">
-        <v>easy</v>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
-      <c r="E18" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F18" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G18" t="str">
-        <v>0.02,0.24</v>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
       </c>
       <c r="H18">
         <v>42921</v>
@@ -921,27 +1704,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>简单-18</v>
-      </c>
-      <c r="C19" t="str">
-        <v>easy</v>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
       </c>
       <c r="D19">
         <v>8</v>
       </c>
-      <c r="E19" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F19" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G19" t="str">
-        <v>0.02,0.24</v>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
       </c>
       <c r="H19">
         <v>43034</v>
@@ -950,27 +1733,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>简单-19</v>
-      </c>
-      <c r="C20" t="str">
-        <v>easy</v>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
-      <c r="E20" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F20" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G20" t="str">
-        <v>0.02,0.24</v>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
       </c>
       <c r="H20">
         <v>43147</v>
@@ -979,27 +1762,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>困难-20</v>
-      </c>
-      <c r="C21" t="str">
-        <v>hard</v>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21" t="str">
-        <v>28,40</v>
-      </c>
-      <c r="F21" t="str">
-        <v>0.20,0.42</v>
-      </c>
-      <c r="G21" t="str">
-        <v>0.06,0.32</v>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
       </c>
       <c r="H21">
         <v>43260</v>
@@ -1009,8 +1792,10 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
+    <ignoredError sqref="A1:I21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -56,6 +56,9 @@
     <t>homeBubbleColorId</t>
   </si>
   <si>
+    <t>inTheoryStep</t>
+  </si>
+  <si>
     <t>简单-01</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>0.00,0.20</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>简单-02</t>
@@ -785,8 +791,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1170,68 +1179,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
   <cols>
-    <col min="2" max="2" width="17.2589285714286" customWidth="1"/>
-    <col min="4" max="4" width="16.3571428571429" customWidth="1"/>
     <col min="5" max="5" width="17.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="12.7857142857143" customWidth="1"/>
     <col min="7" max="7" width="12.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="14.2767857142857" customWidth="1"/>
-    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="13.2410714285714" customWidth="1"/>
+    <col min="10" max="10" width="17.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>41113</v>
@@ -1239,28 +1249,31 @@
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3">
         <v>41226</v>
@@ -1268,28 +1281,31 @@
       <c r="I3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4">
         <v>41339</v>
@@ -1297,28 +1313,31 @@
       <c r="I4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5">
         <v>41452</v>
@@ -1326,28 +1345,31 @@
       <c r="I5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <v>41565</v>
@@ -1355,28 +1377,31 @@
       <c r="I6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>41678</v>
@@ -1384,28 +1409,31 @@
       <c r="I7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8">
         <v>41791</v>
@@ -1413,28 +1441,31 @@
       <c r="I8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9">
         <v>41904</v>
@@ -1442,28 +1473,31 @@
       <c r="I9">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10">
         <v>42017</v>
@@ -1471,28 +1505,31 @@
       <c r="I10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H11">
         <v>42130</v>
@@ -1500,28 +1537,31 @@
       <c r="I11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H12">
         <v>42243</v>
@@ -1529,28 +1569,31 @@
       <c r="I12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H13">
         <v>42356</v>
@@ -1558,28 +1601,31 @@
       <c r="I13">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H14">
         <v>42469</v>
@@ -1587,28 +1633,31 @@
       <c r="I14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H15">
         <v>42582</v>
@@ -1616,28 +1665,31 @@
       <c r="I15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H16">
         <v>42695</v>
@@ -1645,28 +1697,31 @@
       <c r="I16">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H17">
         <v>42808</v>
@@ -1674,28 +1729,31 @@
       <c r="I17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H18">
         <v>42921</v>
@@ -1703,28 +1761,31 @@
       <c r="I18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19">
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H19">
         <v>43034</v>
@@ -1732,28 +1793,31 @@
       <c r="I19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H20">
         <v>43147</v>
@@ -1761,41 +1825,47 @@
       <c r="I20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H21">
         <v>43260</v>
       </c>
       <c r="I21">
         <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I21" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -1,62 +1,543 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView windowWidth="30240" windowHeight="13220"/>
+  </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="48">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>difficulty</t>
+  </si>
+  <si>
+    <t>colorKindCount</t>
+  </si>
+  <si>
+    <t>fruitCountRange</t>
+  </si>
+  <si>
+    <t>radiusRange</t>
+  </si>
+  <si>
+    <t>speedRange</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>homeBubbleColorId</t>
+  </si>
+  <si>
+    <t>inTheoryStep</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>简单-01</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>8,12</t>
+  </si>
+  <si>
+    <t>0.22,0.38</t>
+  </si>
+  <si>
+    <t>0.00,0.20</t>
+  </si>
+  <si>
+    <t>简单-02</t>
+  </si>
+  <si>
+    <t>12,18</t>
+  </si>
+  <si>
+    <t>简单-03</t>
+  </si>
+  <si>
+    <t>14,26</t>
+  </si>
+  <si>
+    <t>简单-04</t>
+  </si>
+  <si>
+    <t>中等-05</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>22,34</t>
+  </si>
+  <si>
+    <t>0.20,0.40</t>
+  </si>
+  <si>
+    <t>0.04,0.28</t>
+  </si>
+  <si>
+    <t>简单-06</t>
+  </si>
+  <si>
+    <t>简单-07</t>
+  </si>
+  <si>
+    <t>简单-08</t>
+  </si>
+  <si>
+    <t>简单-09</t>
+  </si>
+  <si>
+    <t>困难-10</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>28,40</t>
+  </si>
+  <si>
+    <t>0.20,0.42</t>
+  </si>
+  <si>
+    <t>0.06,0.32</t>
+  </si>
+  <si>
+    <t>简单-11</t>
+  </si>
+  <si>
+    <t>18,32</t>
+  </si>
+  <si>
+    <t>0.02,0.24</t>
+  </si>
+  <si>
+    <t>简单-12</t>
+  </si>
+  <si>
+    <t>简单-13</t>
+  </si>
+  <si>
+    <t>简单-14</t>
+  </si>
+  <si>
+    <t>中等-15</t>
+  </si>
+  <si>
+    <t>26,36</t>
+  </si>
+  <si>
+    <t>简单-16</t>
+  </si>
+  <si>
+    <t>简单-17</t>
+  </si>
+  <si>
+    <t>简单-18</t>
+  </si>
+  <si>
+    <t>简单-19</t>
+  </si>
+  <si>
+    <t>困难-20</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -64,18 +545,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -395,67 +1170,75 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="13.6428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>difficulty</v>
-      </c>
-      <c r="D1" t="str">
-        <v>colorKindCount</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fruitCountRange</v>
-      </c>
-      <c r="F1" t="str">
-        <v>radiusRange</v>
-      </c>
-      <c r="G1" t="str">
-        <v>speedRange</v>
-      </c>
-      <c r="H1" t="str">
-        <v>seed</v>
-      </c>
-      <c r="I1" t="str">
-        <v>homeBubbleColorId</v>
-      </c>
-      <c r="J1" t="str">
-        <v>inTheoryStep</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>简单-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>easy</v>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="str">
-        <v>8,12</v>
-      </c>
-      <c r="F2" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0.00,0.20</v>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
       </c>
       <c r="H2">
         <v>41113</v>
@@ -466,28 +1249,32 @@
       <c r="J2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="K2">
+        <f t="shared" ref="K2:K21" si="0">IF(LOWER(C2)="easy",J2+3,IF(LOWER(C2)="medium",J2+2,IF(LOWER(C2)="hard",J2+1,"")))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>简单-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>easy</v>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="str">
-        <v>12,18</v>
-      </c>
-      <c r="F3" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G3" t="str">
-        <v>0.00,0.20</v>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
       <c r="H3">
         <v>41226</v>
@@ -498,28 +1285,32 @@
       <c r="J3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="K3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>简单-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>easy</v>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F4" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G4" t="str">
-        <v>0.00,0.20</v>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4">
         <v>41339</v>
@@ -530,28 +1321,32 @@
       <c r="J4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>简单-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>easy</v>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F5" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G5" t="str">
-        <v>0.00,0.20</v>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
       </c>
       <c r="H5">
         <v>41452</v>
@@ -562,28 +1357,32 @@
       <c r="J5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>中等-05</v>
-      </c>
-      <c r="C6" t="str">
-        <v>medium</v>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" t="str">
-        <v>22,34</v>
-      </c>
-      <c r="F6" t="str">
-        <v>0.20,0.40</v>
-      </c>
-      <c r="G6" t="str">
-        <v>0.04,0.28</v>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
       </c>
       <c r="H6">
         <v>41565</v>
@@ -594,28 +1393,32 @@
       <c r="J6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>简单-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>easy</v>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F7" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G7" t="str">
-        <v>0.00,0.20</v>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
       </c>
       <c r="H7">
         <v>41678</v>
@@ -626,28 +1429,32 @@
       <c r="J7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>简单-07</v>
-      </c>
-      <c r="C8" t="str">
-        <v>easy</v>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
-      <c r="E8" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F8" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G8" t="str">
-        <v>0.00,0.20</v>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
       </c>
       <c r="H8">
         <v>41791</v>
@@ -658,28 +1465,32 @@
       <c r="J8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>简单-08</v>
-      </c>
-      <c r="C9" t="str">
-        <v>easy</v>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F9" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G9" t="str">
-        <v>0.00,0.20</v>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
       </c>
       <c r="H9">
         <v>41904</v>
@@ -690,28 +1501,32 @@
       <c r="J9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>简单-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>easy</v>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F10" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G10" t="str">
-        <v>0.00,0.20</v>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
       </c>
       <c r="H10">
         <v>42017</v>
@@ -722,28 +1537,32 @@
       <c r="J10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>困难-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>hard</v>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="str">
-        <v>28,40</v>
-      </c>
-      <c r="F11" t="str">
-        <v>0.20,0.42</v>
-      </c>
-      <c r="G11" t="str">
-        <v>0.06,0.32</v>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
       </c>
       <c r="H11">
         <v>42130</v>
@@ -754,28 +1573,32 @@
       <c r="J11">
         <v>6</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>简单-11</v>
-      </c>
-      <c r="C12" t="str">
-        <v>easy</v>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F12" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G12" t="str">
-        <v>0.02,0.24</v>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
       </c>
       <c r="H12">
         <v>42243</v>
@@ -786,28 +1609,32 @@
       <c r="J12">
         <v>6</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>简单-12</v>
-      </c>
-      <c r="C13" t="str">
-        <v>easy</v>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F13" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G13" t="str">
-        <v>0.02,0.24</v>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
       </c>
       <c r="H13">
         <v>42356</v>
@@ -818,28 +1645,32 @@
       <c r="J13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>简单-13</v>
-      </c>
-      <c r="C14" t="str">
-        <v>easy</v>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
-      <c r="E14" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F14" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G14" t="str">
-        <v>0.02,0.24</v>
+      <c r="E14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
       </c>
       <c r="H14">
         <v>42469</v>
@@ -850,28 +1681,32 @@
       <c r="J14">
         <v>7</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>简单-14</v>
-      </c>
-      <c r="C15" t="str">
-        <v>easy</v>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F15" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G15" t="str">
-        <v>0.02,0.24</v>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
       </c>
       <c r="H15">
         <v>42582</v>
@@ -882,28 +1717,32 @@
       <c r="J15">
         <v>7</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>中等-15</v>
-      </c>
-      <c r="C16" t="str">
-        <v>medium</v>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
-      <c r="E16" t="str">
-        <v>26,36</v>
-      </c>
-      <c r="F16" t="str">
-        <v>0.20,0.40</v>
-      </c>
-      <c r="G16" t="str">
-        <v>0.04,0.28</v>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
       </c>
       <c r="H16">
         <v>42695</v>
@@ -914,28 +1753,32 @@
       <c r="J16">
         <v>10</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>简单-16</v>
-      </c>
-      <c r="C17" t="str">
-        <v>easy</v>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
-      <c r="E17" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F17" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G17" t="str">
-        <v>0.02,0.24</v>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
       </c>
       <c r="H17">
         <v>42808</v>
@@ -946,28 +1789,32 @@
       <c r="J17">
         <v>7</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>简单-17</v>
-      </c>
-      <c r="C18" t="str">
-        <v>easy</v>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
-      <c r="E18" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F18" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G18" t="str">
-        <v>0.02,0.24</v>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
       </c>
       <c r="H18">
         <v>42921</v>
@@ -978,28 +1825,32 @@
       <c r="J18">
         <v>8</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>简单-18</v>
-      </c>
-      <c r="C19" t="str">
-        <v>easy</v>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
       </c>
       <c r="D19">
         <v>8</v>
       </c>
-      <c r="E19" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F19" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G19" t="str">
-        <v>0.02,0.24</v>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
       </c>
       <c r="H19">
         <v>43034</v>
@@ -1010,28 +1861,32 @@
       <c r="J19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>简单-19</v>
-      </c>
-      <c r="C20" t="str">
-        <v>easy</v>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
-      <c r="E20" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F20" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G20" t="str">
-        <v>0.02,0.24</v>
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
       </c>
       <c r="H20">
         <v>43147</v>
@@ -1042,28 +1897,32 @@
       <c r="J20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>困难-20</v>
-      </c>
-      <c r="C21" t="str">
-        <v>hard</v>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21" t="str">
-        <v>28,40</v>
-      </c>
-      <c r="F21" t="str">
-        <v>0.20,0.42</v>
-      </c>
-      <c r="G21" t="str">
-        <v>0.06,0.32</v>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>34</v>
       </c>
       <c r="H21">
         <v>43260</v>
@@ -1074,10 +1933,16 @@
       <c r="J21">
         <v>13</v>
       </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J21"/>
+    <ignoredError sqref="A1:K21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -469,8 +469,8 @@
       <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2">
-        <f>IF(LOWER(C2)="easy",J2+3,IF(LOWER(C2)="medium",J2+2,IF(LOWER(C2)="hard",J2+1,"")))</f>
+      <c r="K2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -504,8 +504,8 @@
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3">
-        <f>IF(LOWER(C3)="easy",J3+3,IF(LOWER(C3)="medium",J3+2,IF(LOWER(C3)="hard",J3+1,"")))</f>
+      <c r="K3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4">
-        <f>IF(LOWER(C4)="easy",J4+3,IF(LOWER(C4)="medium",J4+2,IF(LOWER(C4)="hard",J4+1,"")))</f>
+        <v>5</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -572,10 +572,10 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <f>IF(LOWER(C5)="easy",J5+3,IF(LOWER(C5)="medium",J5+2,IF(LOWER(C5)="hard",J5+1,"")))</f>
+        <v>6</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -609,8 +609,8 @@
       <c r="J6">
         <v>3</v>
       </c>
-      <c r="K6">
-        <f>IF(LOWER(C6)="easy",J6+3,IF(LOWER(C6)="medium",J6+2,IF(LOWER(C6)="hard",J6+1,"")))</f>
+      <c r="K6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -644,8 +644,8 @@
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7">
-        <f>IF(LOWER(C7)="easy",J7+3,IF(LOWER(C7)="medium",J7+2,IF(LOWER(C7)="hard",J7+1,"")))</f>
+      <c r="K7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -679,8 +679,8 @@
       <c r="J8">
         <v>6</v>
       </c>
-      <c r="K8">
-        <f>IF(LOWER(C8)="easy",J8+3,IF(LOWER(C8)="medium",J8+2,IF(LOWER(C8)="hard",J8+1,"")))</f>
+      <c r="K8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -714,8 +714,8 @@
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
-        <f>IF(LOWER(C9)="easy",J9+3,IF(LOWER(C9)="medium",J9+2,IF(LOWER(C9)="hard",J9+1,"")))</f>
+      <c r="K9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -749,8 +749,8 @@
       <c r="J10">
         <v>6</v>
       </c>
-      <c r="K10">
-        <f>IF(LOWER(C10)="easy",J10+3,IF(LOWER(C10)="medium",J10+2,IF(LOWER(C10)="hard",J10+1,"")))</f>
+      <c r="K10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -784,8 +784,8 @@
       <c r="J11">
         <v>4</v>
       </c>
-      <c r="K11">
-        <f>IF(LOWER(C11)="easy",J11+3,IF(LOWER(C11)="medium",J11+2,IF(LOWER(C11)="hard",J11+1,"")))</f>
+      <c r="K11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -819,8 +819,8 @@
       <c r="J12">
         <v>5</v>
       </c>
-      <c r="K12">
-        <f>IF(LOWER(C12)="easy",J12+3,IF(LOWER(C12)="medium",J12+2,IF(LOWER(C12)="hard",J12+1,"")))</f>
+      <c r="K12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -854,8 +854,8 @@
       <c r="J13">
         <v>4</v>
       </c>
-      <c r="K13">
-        <f>IF(LOWER(C13)="easy",J13+3,IF(LOWER(C13)="medium",J13+2,IF(LOWER(C13)="hard",J13+1,"")))</f>
+      <c r="K13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -889,8 +889,8 @@
       <c r="J14">
         <v>6</v>
       </c>
-      <c r="K14">
-        <f>IF(LOWER(C14)="easy",J14+3,IF(LOWER(C14)="medium",J14+2,IF(LOWER(C14)="hard",J14+1,"")))</f>
+      <c r="K14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -924,8 +924,8 @@
       <c r="J15">
         <v>7</v>
       </c>
-      <c r="K15">
-        <f>IF(LOWER(C15)="easy",J15+3,IF(LOWER(C15)="medium",J15+2,IF(LOWER(C15)="hard",J15+1,"")))</f>
+      <c r="K15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -959,8 +959,8 @@
       <c r="J16">
         <v>6</v>
       </c>
-      <c r="K16">
-        <f>IF(LOWER(C16)="easy",J16+3,IF(LOWER(C16)="medium",J16+2,IF(LOWER(C16)="hard",J16+1,"")))</f>
+      <c r="K16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -994,8 +994,8 @@
       <c r="J17">
         <v>6</v>
       </c>
-      <c r="K17">
-        <f>IF(LOWER(C17)="easy",J17+3,IF(LOWER(C17)="medium",J17+2,IF(LOWER(C17)="hard",J17+1,"")))</f>
+      <c r="K17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1029,8 +1029,8 @@
       <c r="J18">
         <v>7</v>
       </c>
-      <c r="K18">
-        <f>IF(LOWER(C18)="easy",J18+3,IF(LOWER(C18)="medium",J18+2,IF(LOWER(C18)="hard",J18+1,"")))</f>
+      <c r="K18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1064,8 +1064,8 @@
       <c r="J19">
         <v>8</v>
       </c>
-      <c r="K19">
-        <f>IF(LOWER(C19)="easy",J19+3,IF(LOWER(C19)="medium",J19+2,IF(LOWER(C19)="hard",J19+1,"")))</f>
+      <c r="K19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1099,8 +1099,8 @@
       <c r="J20">
         <v>8</v>
       </c>
-      <c r="K20">
-        <f>IF(LOWER(C20)="easy",J20+3,IF(LOWER(C20)="medium",J20+2,IF(LOWER(C20)="hard",J20+1,"")))</f>
+      <c r="K20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1134,8 +1134,8 @@
       <c r="J21">
         <v>9</v>
       </c>
-      <c r="K21">
-        <f>IF(LOWER(C21)="easy",J21+3,IF(LOWER(C21)="medium",J21+2,IF(LOWER(C21)="hard",J21+1,"")))</f>
+      <c r="K21" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -607,7 +607,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -642,7 +642,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -677,7 +677,7 @@
         <v>2</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -712,7 +712,7 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -747,7 +747,7 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -852,7 +852,7 @@
         <v>2</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -922,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" t="str">
         <v/>

--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -469,8 +469,8 @@
       <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2">
-        <f>IF(LOWER(C2)="easy",J2+3,IF(LOWER(C2)="medium",J2+2,IF(LOWER(C2)="hard",J2+1,"")))</f>
+      <c r="K2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -504,8 +504,8 @@
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3">
-        <f>IF(LOWER(C3)="easy",J3+3,IF(LOWER(C3)="medium",J3+2,IF(LOWER(C3)="hard",J3+1,"")))</f>
+      <c r="K3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -539,8 +539,8 @@
       <c r="J4">
         <v>4</v>
       </c>
-      <c r="K4">
-        <f>IF(LOWER(C4)="easy",J4+3,IF(LOWER(C4)="medium",J4+2,IF(LOWER(C4)="hard",J4+1,"")))</f>
+      <c r="K4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -574,8 +574,8 @@
       <c r="J5">
         <v>5</v>
       </c>
-      <c r="K5">
-        <f>IF(LOWER(C5)="easy",J5+3,IF(LOWER(C5)="medium",J5+2,IF(LOWER(C5)="hard",J5+1,"")))</f>
+      <c r="K5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -609,8 +609,8 @@
       <c r="J6">
         <v>3</v>
       </c>
-      <c r="K6">
-        <f>IF(LOWER(C6)="easy",J6+3,IF(LOWER(C6)="medium",J6+2,IF(LOWER(C6)="hard",J6+1,"")))</f>
+      <c r="K6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -644,8 +644,8 @@
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7">
-        <f>IF(LOWER(C7)="easy",J7+3,IF(LOWER(C7)="medium",J7+2,IF(LOWER(C7)="hard",J7+1,"")))</f>
+      <c r="K7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -679,8 +679,8 @@
       <c r="J8">
         <v>6</v>
       </c>
-      <c r="K8">
-        <f>IF(LOWER(C8)="easy",J8+3,IF(LOWER(C8)="medium",J8+2,IF(LOWER(C8)="hard",J8+1,"")))</f>
+      <c r="K8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -714,8 +714,8 @@
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
-        <f>IF(LOWER(C9)="easy",J9+3,IF(LOWER(C9)="medium",J9+2,IF(LOWER(C9)="hard",J9+1,"")))</f>
+      <c r="K9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -749,8 +749,8 @@
       <c r="J10">
         <v>6</v>
       </c>
-      <c r="K10">
-        <f>IF(LOWER(C10)="easy",J10+3,IF(LOWER(C10)="medium",J10+2,IF(LOWER(C10)="hard",J10+1,"")))</f>
+      <c r="K10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -784,8 +784,8 @@
       <c r="J11">
         <v>4</v>
       </c>
-      <c r="K11">
-        <f>IF(LOWER(C11)="easy",J11+3,IF(LOWER(C11)="medium",J11+2,IF(LOWER(C11)="hard",J11+1,"")))</f>
+      <c r="K11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -819,8 +819,8 @@
       <c r="J12">
         <v>5</v>
       </c>
-      <c r="K12">
-        <f>IF(LOWER(C12)="easy",J12+3,IF(LOWER(C12)="medium",J12+2,IF(LOWER(C12)="hard",J12+1,"")))</f>
+      <c r="K12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -854,8 +854,8 @@
       <c r="J13">
         <v>4</v>
       </c>
-      <c r="K13">
-        <f>IF(LOWER(C13)="easy",J13+3,IF(LOWER(C13)="medium",J13+2,IF(LOWER(C13)="hard",J13+1,"")))</f>
+      <c r="K13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -889,8 +889,8 @@
       <c r="J14">
         <v>6</v>
       </c>
-      <c r="K14">
-        <f>IF(LOWER(C14)="easy",J14+3,IF(LOWER(C14)="medium",J14+2,IF(LOWER(C14)="hard",J14+1,"")))</f>
+      <c r="K14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -924,8 +924,8 @@
       <c r="J15">
         <v>7</v>
       </c>
-      <c r="K15">
-        <f>IF(LOWER(C15)="easy",J15+3,IF(LOWER(C15)="medium",J15+2,IF(LOWER(C15)="hard",J15+1,"")))</f>
+      <c r="K15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -959,8 +959,8 @@
       <c r="J16">
         <v>6</v>
       </c>
-      <c r="K16">
-        <f>IF(LOWER(C16)="easy",J16+3,IF(LOWER(C16)="medium",J16+2,IF(LOWER(C16)="hard",J16+1,"")))</f>
+      <c r="K16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -994,8 +994,8 @@
       <c r="J17">
         <v>6</v>
       </c>
-      <c r="K17">
-        <f>IF(LOWER(C17)="easy",J17+3,IF(LOWER(C17)="medium",J17+2,IF(LOWER(C17)="hard",J17+1,"")))</f>
+      <c r="K17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1029,8 +1029,8 @@
       <c r="J18">
         <v>7</v>
       </c>
-      <c r="K18">
-        <f>IF(LOWER(C18)="easy",J18+3,IF(LOWER(C18)="medium",J18+2,IF(LOWER(C18)="hard",J18+1,"")))</f>
+      <c r="K18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1064,8 +1064,8 @@
       <c r="J19">
         <v>8</v>
       </c>
-      <c r="K19">
-        <f>IF(LOWER(C19)="easy",J19+3,IF(LOWER(C19)="medium",J19+2,IF(LOWER(C19)="hard",J19+1,"")))</f>
+      <c r="K19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1099,8 +1099,8 @@
       <c r="J20">
         <v>8</v>
       </c>
-      <c r="K20">
-        <f>IF(LOWER(C20)="easy",J20+3,IF(LOWER(C20)="medium",J20+2,IF(LOWER(C20)="hard",J20+1,"")))</f>
+      <c r="K20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1134,8 +1134,8 @@
       <c r="J21">
         <v>9</v>
       </c>
-      <c r="K21">
-        <f>IF(LOWER(C21)="easy",J21+3,IF(LOWER(C21)="medium",J21+2,IF(LOWER(C21)="hard",J21+1,"")))</f>
+      <c r="K21" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -1,50 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengbotao/fruit/src/excel/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB488DC-9E3A-4347-B011-0E98E51804A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="24020" yWindow="-23300" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="49">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>difficulty</t>
+  </si>
+  <si>
+    <t>colorKindCount</t>
+  </si>
+  <si>
+    <t>fruitCountRange</t>
+  </si>
+  <si>
+    <t>radiusRange</t>
+  </si>
+  <si>
+    <t>speedRange</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>homeBubbleColorId</t>
+  </si>
+  <si>
+    <t>inTheoryStep</t>
+  </si>
+  <si>
+    <t>简单-01</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>8,12</t>
+  </si>
+  <si>
+    <t>0.22,0.38</t>
+  </si>
+  <si>
+    <t>0.00,0.20</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>简单-02</t>
+  </si>
+  <si>
+    <t>12,18</t>
+  </si>
+  <si>
+    <t>简单-03</t>
+  </si>
+  <si>
+    <t>14,26</t>
+  </si>
+  <si>
+    <t>简单-04</t>
+  </si>
+  <si>
+    <t>中等-05</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>22,34</t>
+  </si>
+  <si>
+    <t>0.20,0.40</t>
+  </si>
+  <si>
+    <t>0.04,0.28</t>
+  </si>
+  <si>
+    <t>简单-06</t>
+  </si>
+  <si>
+    <t>简单-07</t>
+  </si>
+  <si>
+    <t>简单-08</t>
+  </si>
+  <si>
+    <t>简单-09</t>
+  </si>
+  <si>
+    <t>困难-10</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>28,40</t>
+  </si>
+  <si>
+    <t>0.20,0.42</t>
+  </si>
+  <si>
+    <t>0.06,0.32</t>
+  </si>
+  <si>
+    <t>简单-11</t>
+  </si>
+  <si>
+    <t>18,32</t>
+  </si>
+  <si>
+    <t>0.02,0.24</t>
+  </si>
+  <si>
+    <t>简单-12</t>
+  </si>
+  <si>
+    <t>简单-13</t>
+  </si>
+  <si>
+    <t>简单-14</t>
+  </si>
+  <si>
+    <t>中等-15</t>
+  </si>
+  <si>
+    <t>26,36</t>
+  </si>
+  <si>
+    <t>简单-16</t>
+  </si>
+  <si>
+    <t>简单-17</t>
+  </si>
+  <si>
+    <t>简单-18</t>
+  </si>
+  <si>
+    <t>简单-19</t>
+  </si>
+  <si>
+    <t>困难-20</t>
+  </si>
+  <si>
+    <t>step</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -69,13 +211,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -400,65 +550,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>difficulty</v>
-      </c>
-      <c r="D1" t="str">
-        <v>colorKindCount</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fruitCountRange</v>
-      </c>
-      <c r="F1" t="str">
-        <v>radiusRange</v>
-      </c>
-      <c r="G1" t="str">
-        <v>speedRange</v>
-      </c>
-      <c r="H1" t="str">
-        <v>seed</v>
-      </c>
-      <c r="I1" t="str">
-        <v>homeBubbleColorId</v>
-      </c>
-      <c r="J1" t="str">
-        <v>inTheoryStep</v>
-      </c>
-      <c r="K1" t="str">
-        <v>step</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>简单-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>easy</v>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="str">
-        <v>8,12</v>
-      </c>
-      <c r="F2" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0.00,0.20</v>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
       </c>
       <c r="H2">
         <v>41113</v>
@@ -469,31 +620,31 @@
       <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>简单-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>easy</v>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="str">
-        <v>12,18</v>
-      </c>
-      <c r="F3" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G3" t="str">
-        <v>0.00,0.20</v>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
       </c>
       <c r="H3">
         <v>41226</v>
@@ -504,31 +655,31 @@
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>简单-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>easy</v>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F4" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G4" t="str">
-        <v>0.00,0.20</v>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
       </c>
       <c r="H4">
         <v>41339</v>
@@ -539,31 +690,31 @@
       <c r="J4">
         <v>5</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>简单-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>easy</v>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F5" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G5" t="str">
-        <v>0.00,0.20</v>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
       </c>
       <c r="H5">
         <v>41452</v>
@@ -572,33 +723,33 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
+        <v>4</v>
+      </c>
+      <c r="K5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>中等-05</v>
-      </c>
-      <c r="C6" t="str">
-        <v>medium</v>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" t="str">
-        <v>22,34</v>
-      </c>
-      <c r="F6" t="str">
-        <v>0.20,0.40</v>
-      </c>
-      <c r="G6" t="str">
-        <v>0.04,0.28</v>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
       </c>
       <c r="H6">
         <v>41565</v>
@@ -609,31 +760,31 @@
       <c r="J6">
         <v>5</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>简单-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>easy</v>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F7" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G7" t="str">
-        <v>0.00,0.20</v>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
       </c>
       <c r="H7">
         <v>41678</v>
@@ -642,33 +793,33 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>简单-07</v>
-      </c>
-      <c r="C8" t="str">
-        <v>easy</v>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
-      <c r="E8" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F8" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G8" t="str">
-        <v>0.00,0.20</v>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
       </c>
       <c r="H8">
         <v>41791</v>
@@ -677,33 +828,33 @@
         <v>2</v>
       </c>
       <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
+        <v>9</v>
+      </c>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>简单-08</v>
-      </c>
-      <c r="C9" t="str">
-        <v>easy</v>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F9" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G9" t="str">
-        <v>0.00,0.20</v>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
       </c>
       <c r="H9">
         <v>41904</v>
@@ -712,33 +863,33 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <v>6</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>简单-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>easy</v>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" t="str">
-        <v>14,26</v>
-      </c>
-      <c r="F10" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G10" t="str">
-        <v>0.00,0.20</v>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
       </c>
       <c r="H10">
         <v>42017</v>
@@ -747,33 +898,33 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>9</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>困难-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>hard</v>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="str">
-        <v>28,40</v>
-      </c>
-      <c r="F11" t="str">
-        <v>0.20,0.42</v>
-      </c>
-      <c r="G11" t="str">
-        <v>0.06,0.32</v>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
       </c>
       <c r="H11">
         <v>42130</v>
@@ -782,33 +933,33 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>7</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
+        <v>8</v>
+      </c>
+      <c r="K11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>简单-11</v>
-      </c>
-      <c r="C12" t="str">
-        <v>easy</v>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F12" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G12" t="str">
-        <v>0.02,0.24</v>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
       </c>
       <c r="H12">
         <v>42243</v>
@@ -819,31 +970,31 @@
       <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>简单-12</v>
-      </c>
-      <c r="C13" t="str">
-        <v>easy</v>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F13" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G13" t="str">
-        <v>0.02,0.24</v>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
       </c>
       <c r="H13">
         <v>42356</v>
@@ -854,31 +1005,31 @@
       <c r="J13">
         <v>6</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>简单-13</v>
-      </c>
-      <c r="C14" t="str">
-        <v>easy</v>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
-      <c r="E14" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F14" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G14" t="str">
-        <v>0.02,0.24</v>
+      <c r="E14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
       </c>
       <c r="H14">
         <v>42469</v>
@@ -889,31 +1040,31 @@
       <c r="J14">
         <v>7</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>简单-14</v>
-      </c>
-      <c r="C15" t="str">
-        <v>easy</v>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F15" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G15" t="str">
-        <v>0.02,0.24</v>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
       </c>
       <c r="H15">
         <v>42582</v>
@@ -922,33 +1073,33 @@
         <v>5</v>
       </c>
       <c r="J15">
-        <v>8</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
+        <v>12</v>
+      </c>
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>中等-15</v>
-      </c>
-      <c r="C16" t="str">
-        <v>medium</v>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
-      <c r="E16" t="str">
-        <v>26,36</v>
-      </c>
-      <c r="F16" t="str">
-        <v>0.20,0.40</v>
-      </c>
-      <c r="G16" t="str">
-        <v>0.04,0.28</v>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
       </c>
       <c r="H16">
         <v>42695</v>
@@ -957,33 +1108,33 @@
         <v>4</v>
       </c>
       <c r="J16">
-        <v>6</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
+        <v>11</v>
+      </c>
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>简单-16</v>
-      </c>
-      <c r="C17" t="str">
-        <v>easy</v>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
-      <c r="E17" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F17" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G17" t="str">
-        <v>0.02,0.24</v>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
       </c>
       <c r="H17">
         <v>42808</v>
@@ -992,33 +1143,33 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>6</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
+        <v>8</v>
+      </c>
+      <c r="K17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>简单-17</v>
-      </c>
-      <c r="C18" t="str">
-        <v>easy</v>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
-      <c r="E18" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F18" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G18" t="str">
-        <v>0.02,0.24</v>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>37</v>
       </c>
       <c r="H18">
         <v>42921</v>
@@ -1027,33 +1178,33 @@
         <v>2</v>
       </c>
       <c r="J18">
-        <v>7</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
+        <v>8</v>
+      </c>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>简单-18</v>
-      </c>
-      <c r="C19" t="str">
-        <v>easy</v>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
       </c>
       <c r="D19">
         <v>8</v>
       </c>
-      <c r="E19" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F19" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G19" t="str">
-        <v>0.02,0.24</v>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
       </c>
       <c r="H19">
         <v>43034</v>
@@ -1062,33 +1213,33 @@
         <v>3</v>
       </c>
       <c r="J19">
-        <v>8</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
+        <v>13</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>简单-19</v>
-      </c>
-      <c r="C20" t="str">
-        <v>easy</v>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
-      <c r="E20" t="str">
-        <v>18,32</v>
-      </c>
-      <c r="F20" t="str">
-        <v>0.22,0.38</v>
-      </c>
-      <c r="G20" t="str">
-        <v>0.02,0.24</v>
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
       </c>
       <c r="H20">
         <v>43147</v>
@@ -1097,33 +1248,33 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>8</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
+        <v>12</v>
+      </c>
+      <c r="K20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>困难-20</v>
-      </c>
-      <c r="C21" t="str">
-        <v>hard</v>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21" t="str">
-        <v>28,40</v>
-      </c>
-      <c r="F21" t="str">
-        <v>0.20,0.42</v>
-      </c>
-      <c r="G21" t="str">
-        <v>0.06,0.32</v>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>34</v>
       </c>
       <c r="H21">
         <v>43260</v>
@@ -1132,15 +1283,17 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>9</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
+        <v>17</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
+    <ignoredError sqref="A2:K21 A1:J1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengbotao/fruit/src/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB488DC-9E3A-4347-B011-0E98E51804A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D189B3BE-9408-E04E-9474-3544991CAF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24020" yWindow="-23300" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25340" yWindow="-25880" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -52,6 +52,12 @@
     <t>inTheoryStep</t>
   </si>
   <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>lockedBubbles</t>
+  </si>
+  <si>
     <t>简单-01</t>
   </si>
   <si>
@@ -166,7 +172,7 @@
     <t>困难-20</t>
   </si>
   <si>
-    <t>step</t>
+    <t>0:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -210,8 +216,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -551,10 +558,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="12" max="12" width="10.83203125" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -586,30 +596,33 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>41113</v>
@@ -618,33 +631,33 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3">
         <v>41226</v>
@@ -656,30 +669,33 @@
         <v>3</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H4">
         <v>41339</v>
@@ -691,30 +707,33 @@
         <v>5</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5">
         <v>41452</v>
@@ -726,30 +745,33 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6">
         <v>41565</v>
@@ -761,30 +783,33 @@
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7">
         <v>41678</v>
@@ -796,30 +821,33 @@
         <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8">
         <v>41791</v>
@@ -831,30 +859,33 @@
         <v>9</v>
       </c>
       <c r="K8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9">
         <v>41904</v>
@@ -866,30 +897,33 @@
         <v>4</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H10">
         <v>42017</v>
@@ -901,30 +935,33 @@
         <v>8</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H11">
         <v>42130</v>
@@ -936,30 +973,33 @@
         <v>8</v>
       </c>
       <c r="K11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H12">
         <v>42243</v>
@@ -971,30 +1011,33 @@
         <v>6</v>
       </c>
       <c r="K12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H13">
         <v>42356</v>
@@ -1006,30 +1049,33 @@
         <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H14">
         <v>42469</v>
@@ -1041,30 +1087,33 @@
         <v>7</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H15">
         <v>42582</v>
@@ -1076,30 +1125,33 @@
         <v>12</v>
       </c>
       <c r="K15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H16">
         <v>42695</v>
@@ -1111,30 +1163,33 @@
         <v>11</v>
       </c>
       <c r="K16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H17">
         <v>42808</v>
@@ -1146,30 +1201,33 @@
         <v>8</v>
       </c>
       <c r="K17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H18">
         <v>42921</v>
@@ -1181,30 +1239,33 @@
         <v>8</v>
       </c>
       <c r="K18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19">
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H19">
         <v>43034</v>
@@ -1216,30 +1277,33 @@
         <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H20">
         <v>43147</v>
@@ -1251,30 +1315,33 @@
         <v>12</v>
       </c>
       <c r="K20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>17</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21">
         <v>43260</v>
@@ -1286,14 +1353,17 @@
         <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:K21 A1:J1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L1 A3:L6 A2:K2 A8:L21 A7:K7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -454,10 +454,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="str">
-        <v>8,12</v>
+        <v>10,12</v>
       </c>
       <c r="F2" t="str">
-        <v>0.22,0.38</v>
+        <v>0.15,0.2</v>
       </c>
       <c r="G2" t="str">
         <v>0.00,0.20</v>
@@ -469,7 +469,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -478,7 +478,7 @@
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>2,5</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         <v>3</v>
       </c>
       <c r="E3" t="str">
-        <v>12,18</v>
+        <v>11,13</v>
       </c>
       <c r="F3" t="str">
-        <v>0.22,0.38</v>
+        <v>0.15,0.2</v>
       </c>
       <c r="G3" t="str">
         <v>0.00,0.20</v>
@@ -536,10 +536,10 @@
         <v>3</v>
       </c>
       <c r="E4" t="str">
-        <v>14,26</v>
+        <v>12,14</v>
       </c>
       <c r="F4" t="str">
-        <v>0.22,0.38</v>
+        <v>0.15,0.2</v>
       </c>
       <c r="G4" t="str">
         <v>0.00,0.20</v>
@@ -551,7 +551,7 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -574,13 +574,13 @@
         <v>easy</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="str">
-        <v>14,26</v>
+        <v>13,15</v>
       </c>
       <c r="F5" t="str">
-        <v>0.22,0.38</v>
+        <v>0.15,0.2</v>
       </c>
       <c r="G5" t="str">
         <v>0.00,0.20</v>
@@ -592,7 +592,7 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -615,13 +615,13 @@
         <v>medium</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="str">
-        <v>22,34</v>
+        <v>15,20</v>
       </c>
       <c r="F6" t="str">
-        <v>0.20,0.40</v>
+        <v>0.15,0.2</v>
       </c>
       <c r="G6" t="str">
         <v>0.04,0.28</v>
@@ -633,7 +633,7 @@
         <v>4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -659,10 +659,10 @@
         <v>4</v>
       </c>
       <c r="E7" t="str">
-        <v>14,26</v>
+        <v>14,17</v>
       </c>
       <c r="F7" t="str">
-        <v>0.22,0.38</v>
+        <v>0.12,0.24</v>
       </c>
       <c r="G7" t="str">
         <v>0.00,0.20</v>
@@ -674,13 +674,13 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>0:3</v>
+        <v>1:5</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -700,10 +700,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="str">
-        <v>14,26</v>
+        <v>15,18</v>
       </c>
       <c r="F8" t="str">
-        <v>0.22,0.38</v>
+        <v>0.12,0.24</v>
       </c>
       <c r="G8" t="str">
         <v>0.00,0.20</v>
@@ -715,13 +715,13 @@
         <v>2</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K8" t="str">
         <v/>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>3:8</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -738,13 +738,13 @@
         <v>easy</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="str">
-        <v>14,26</v>
+        <v>16,19</v>
       </c>
       <c r="F9" t="str">
-        <v>0.22,0.38</v>
+        <v>0.12,0.24</v>
       </c>
       <c r="G9" t="str">
         <v>0.00,0.20</v>
@@ -756,13 +756,13 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>2:5;7:8</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -782,10 +782,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="str">
-        <v>14,26</v>
+        <v>17,20</v>
       </c>
       <c r="F10" t="str">
-        <v>0.22,0.38</v>
+        <v>0.12,0.24</v>
       </c>
       <c r="G10" t="str">
         <v>0.00,0.20</v>
@@ -797,13 +797,13 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>3:6;8:10</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -820,13 +820,13 @@
         <v>hard</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="str">
-        <v>28,40</v>
+        <v>20,25</v>
       </c>
       <c r="F11" t="str">
-        <v>0.20,0.42</v>
+        <v>0.12,0.24</v>
       </c>
       <c r="G11" t="str">
         <v>0.06,0.32</v>
@@ -844,7 +844,7 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>2:6;7:8;12:12</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -864,10 +864,10 @@
         <v>5</v>
       </c>
       <c r="E12" t="str">
-        <v>18,32</v>
+        <v>17,21</v>
       </c>
       <c r="F12" t="str">
-        <v>0.22,0.38</v>
+        <v>0.1,0.28</v>
       </c>
       <c r="G12" t="str">
         <v>0.02,0.24</v>
@@ -887,8 +887,8 @@
       <c r="L12" t="str">
         <v/>
       </c>
-      <c r="M12" t="str">
-        <v/>
+      <c r="M12">
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -902,13 +902,13 @@
         <v>easy</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="str">
-        <v>18,32</v>
+        <v>18,22</v>
       </c>
       <c r="F13" t="str">
-        <v>0.22,0.38</v>
+        <v>0.1,0.28</v>
       </c>
       <c r="G13" t="str">
         <v>0.02,0.24</v>
@@ -920,16 +920,16 @@
         <v>2</v>
       </c>
       <c r="J13">
+        <v>7</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13">
         <v>6</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -943,13 +943,13 @@
         <v>easy</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="str">
-        <v>18,32</v>
+        <v>18,22</v>
       </c>
       <c r="F14" t="str">
-        <v>0.22,0.38</v>
+        <v>0.1,0.28</v>
       </c>
       <c r="G14" t="str">
         <v>0.02,0.24</v>
@@ -961,7 +961,7 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -969,8 +969,8 @@
       <c r="L14" t="str">
         <v/>
       </c>
-      <c r="M14" t="str">
-        <v/>
+      <c r="M14">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -987,10 +987,10 @@
         <v>6</v>
       </c>
       <c r="E15" t="str">
-        <v>18,32</v>
+        <v>19,23</v>
       </c>
       <c r="F15" t="str">
-        <v>0.22,0.38</v>
+        <v>0.1,0.28</v>
       </c>
       <c r="G15" t="str">
         <v>0.02,0.24</v>
@@ -1002,7 +1002,7 @@
         <v>5</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1011,7 +1011,7 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2,8</v>
       </c>
     </row>
     <row r="16">
@@ -1025,13 +1025,13 @@
         <v>medium</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="str">
-        <v>26,36</v>
+        <v>20,25</v>
       </c>
       <c r="F16" t="str">
-        <v>0.20,0.40</v>
+        <v>0.1,0.28</v>
       </c>
       <c r="G16" t="str">
         <v>0.04,0.28</v>
@@ -1043,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="J16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1052,7 +1052,7 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2,6,10</v>
       </c>
     </row>
     <row r="17">
@@ -1069,10 +1069,10 @@
         <v>6</v>
       </c>
       <c r="E17" t="str">
-        <v>18,32</v>
+        <v>20,26</v>
       </c>
       <c r="F17" t="str">
-        <v>0.22,0.38</v>
+        <v>0.07,0.32</v>
       </c>
       <c r="G17" t="str">
         <v>0.02,0.24</v>
@@ -1084,16 +1084,16 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v/>
+        <v>6:6</v>
+      </c>
+      <c r="M17">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1107,13 +1107,13 @@
         <v>easy</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" t="str">
-        <v>18,32</v>
+        <v>20,26</v>
       </c>
       <c r="F18" t="str">
-        <v>0.22,0.38</v>
+        <v>0.07,0.32</v>
       </c>
       <c r="G18" t="str">
         <v>0.02,0.24</v>
@@ -1125,16 +1125,16 @@
         <v>2</v>
       </c>
       <c r="J18">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
+        <v>6:10;15:6</v>
+      </c>
+      <c r="M18">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1148,13 +1148,13 @@
         <v>easy</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="str">
-        <v>18,32</v>
+        <v>21,28</v>
       </c>
       <c r="F19" t="str">
-        <v>0.22,0.38</v>
+        <v>0.07,0.32</v>
       </c>
       <c r="G19" t="str">
         <v>0.02,0.24</v>
@@ -1166,16 +1166,16 @@
         <v>3</v>
       </c>
       <c r="J19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>6:14;18:6</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>3,9</v>
       </c>
     </row>
     <row r="20">
@@ -1192,10 +1192,10 @@
         <v>7</v>
       </c>
       <c r="E20" t="str">
-        <v>18,32</v>
+        <v>21,28</v>
       </c>
       <c r="F20" t="str">
-        <v>0.22,0.38</v>
+        <v>0.07,0.32</v>
       </c>
       <c r="G20" t="str">
         <v>0.02,0.24</v>
@@ -1207,16 +1207,16 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>5:8;12:10;18:18</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2,8</v>
       </c>
     </row>
     <row r="21">
@@ -1233,10 +1233,10 @@
         <v>8</v>
       </c>
       <c r="E21" t="str">
-        <v>28,40</v>
+        <v>30,35</v>
       </c>
       <c r="F21" t="str">
-        <v>0.20,0.42</v>
+        <v>0.07,0.32</v>
       </c>
       <c r="G21" t="str">
         <v>0.06,0.32</v>
@@ -1248,16 +1248,16 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>7:8;15:12;23:14</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>3,8,13</v>
       </c>
     </row>
   </sheetData>

--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -1,46 +1,269 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengbotao/fruit/src/excel/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78567EF-63CF-244A-9F7C-88C87D50CC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="25200" yWindow="-24160" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="75">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>difficulty</t>
+  </si>
+  <si>
+    <t>colorKindCount</t>
+  </si>
+  <si>
+    <t>fruitCountRange</t>
+  </si>
+  <si>
+    <t>radiusRange</t>
+  </si>
+  <si>
+    <t>speedRange</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>homeBubbleColorId</t>
+  </si>
+  <si>
+    <t>inTheoryStep</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>lockedBubbles</t>
+  </si>
+  <si>
+    <t>doubleLayerBubbles</t>
+  </si>
+  <si>
+    <t>简单-01</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>10,12</t>
+  </si>
+  <si>
+    <t>0.15,0.2</t>
+  </si>
+  <si>
+    <t>0.00,0.20</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>简单-02</t>
+  </si>
+  <si>
+    <t>11,13</t>
+  </si>
+  <si>
+    <t>简单-03</t>
+  </si>
+  <si>
+    <t>12,14</t>
+  </si>
+  <si>
+    <t>简单-04</t>
+  </si>
+  <si>
+    <t>13,15</t>
+  </si>
+  <si>
+    <t>中等-05</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>15,20</t>
+  </si>
+  <si>
+    <t>0.04,0.28</t>
+  </si>
+  <si>
+    <t>简单-06</t>
+  </si>
+  <si>
+    <t>14,17</t>
+  </si>
+  <si>
+    <t>0.12,0.24</t>
+  </si>
+  <si>
+    <t>1:5</t>
+  </si>
+  <si>
+    <t>简单-07</t>
+  </si>
+  <si>
+    <t>15,18</t>
+  </si>
+  <si>
+    <t>3:8</t>
+  </si>
+  <si>
+    <t>简单-08</t>
+  </si>
+  <si>
+    <t>16,19</t>
+  </si>
+  <si>
+    <t>2:5;7:8</t>
+  </si>
+  <si>
+    <t>简单-09</t>
+  </si>
+  <si>
+    <t>17,20</t>
+  </si>
+  <si>
+    <t>3:6;8:10</t>
+  </si>
+  <si>
+    <t>困难-10</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>20,25</t>
+  </si>
+  <si>
+    <t>0.06,0.32</t>
+  </si>
+  <si>
+    <t>2:6;7:8;12:12</t>
+  </si>
+  <si>
+    <t>简单-11</t>
+  </si>
+  <si>
+    <t>17,21</t>
+  </si>
+  <si>
+    <t>0.1,0.28</t>
+  </si>
+  <si>
+    <t>0.02,0.24</t>
+  </si>
+  <si>
+    <t>简单-12</t>
+  </si>
+  <si>
+    <t>18,22</t>
+  </si>
+  <si>
+    <t>简单-13</t>
+  </si>
+  <si>
+    <t>简单-14</t>
+  </si>
+  <si>
+    <t>19,23</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>中等-15</t>
+  </si>
+  <si>
+    <t>2,6,10</t>
+  </si>
+  <si>
+    <t>简单-16</t>
+  </si>
+  <si>
+    <t>20,26</t>
+  </si>
+  <si>
+    <t>0.07,0.32</t>
+  </si>
+  <si>
+    <t>6:6</t>
+  </si>
+  <si>
+    <t>简单-17</t>
+  </si>
+  <si>
+    <t>6:10;15:6</t>
+  </si>
+  <si>
+    <t>简单-18</t>
+  </si>
+  <si>
+    <t>21,28</t>
+  </si>
+  <si>
+    <t>6:14;18:6</t>
+  </si>
+  <si>
+    <t>3,9</t>
+  </si>
+  <si>
+    <t>简单-19</t>
+  </si>
+  <si>
+    <t>5:8;12:10;18:18</t>
+  </si>
+  <si>
+    <t>困难-20</t>
+  </si>
+  <si>
+    <t>30,35</t>
+  </si>
+  <si>
+    <t>7:8;15:12;23:14</t>
+  </si>
+  <si>
+    <t>3,8,13</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,13 +288,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,71 +627,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>difficulty</v>
-      </c>
-      <c r="D1" t="str">
-        <v>colorKindCount</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fruitCountRange</v>
-      </c>
-      <c r="F1" t="str">
-        <v>radiusRange</v>
-      </c>
-      <c r="G1" t="str">
-        <v>speedRange</v>
-      </c>
-      <c r="H1" t="str">
-        <v>seed</v>
-      </c>
-      <c r="I1" t="str">
-        <v>homeBubbleColorId</v>
-      </c>
-      <c r="J1" t="str">
-        <v>inTheoryStep</v>
-      </c>
-      <c r="K1" t="str">
-        <v>step</v>
-      </c>
-      <c r="L1" t="str">
-        <v>lockedBubbles</v>
-      </c>
-      <c r="M1" t="str">
-        <v>doubleLayerBubbles</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>简单-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>easy</v>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="str">
-        <v>10,12</v>
-      </c>
-      <c r="F2" t="str">
-        <v>0.15,0.2</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0.00,0.20</v>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
       </c>
       <c r="H2">
         <v>41113</v>
@@ -471,37 +703,37 @@
       <c r="J2">
         <v>3</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>简单-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>easy</v>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="str">
-        <v>11,13</v>
-      </c>
-      <c r="F3" t="str">
-        <v>0.15,0.2</v>
-      </c>
-      <c r="G3" t="str">
-        <v>0.00,0.20</v>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
       </c>
       <c r="H3">
         <v>41226</v>
@@ -512,37 +744,37 @@
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>简单-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>easy</v>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" t="str">
-        <v>12,14</v>
-      </c>
-      <c r="F4" t="str">
-        <v>0.15,0.2</v>
-      </c>
-      <c r="G4" t="str">
-        <v>0.00,0.20</v>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
       </c>
       <c r="H4">
         <v>41339</v>
@@ -553,37 +785,37 @@
       <c r="J4">
         <v>3</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>简单-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>easy</v>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5" t="str">
-        <v>13,15</v>
-      </c>
-      <c r="F5" t="str">
-        <v>0.15,0.2</v>
-      </c>
-      <c r="G5" t="str">
-        <v>0.00,0.20</v>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
       </c>
       <c r="H5">
         <v>41452</v>
@@ -594,37 +826,37 @@
       <c r="J5">
         <v>3</v>
       </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>中等-05</v>
-      </c>
-      <c r="C6" t="str">
-        <v>medium</v>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" t="str">
-        <v>15,20</v>
-      </c>
-      <c r="F6" t="str">
-        <v>0.15,0.2</v>
-      </c>
-      <c r="G6" t="str">
-        <v>0.04,0.28</v>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
       </c>
       <c r="H6">
         <v>41565</v>
@@ -635,37 +867,37 @@
       <c r="J6">
         <v>4</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>简单-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>easy</v>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="str">
-        <v>14,17</v>
-      </c>
-      <c r="F7" t="str">
-        <v>0.12,0.24</v>
-      </c>
-      <c r="G7" t="str">
-        <v>0.00,0.20</v>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
       </c>
       <c r="H7">
         <v>41678</v>
@@ -676,37 +908,37 @@
       <c r="J7">
         <v>4</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>1:5</v>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>简单-07</v>
-      </c>
-      <c r="C8" t="str">
-        <v>easy</v>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
-      <c r="E8" t="str">
-        <v>15,18</v>
-      </c>
-      <c r="F8" t="str">
-        <v>0.12,0.24</v>
-      </c>
-      <c r="G8" t="str">
-        <v>0.00,0.20</v>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
       </c>
       <c r="H8">
         <v>41791</v>
@@ -717,37 +949,37 @@
       <c r="J8">
         <v>7</v>
       </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>3:8</v>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>简单-08</v>
-      </c>
-      <c r="C9" t="str">
-        <v>easy</v>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
-      <c r="E9" t="str">
-        <v>16,19</v>
-      </c>
-      <c r="F9" t="str">
-        <v>0.12,0.24</v>
-      </c>
-      <c r="G9" t="str">
-        <v>0.00,0.20</v>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
       </c>
       <c r="H9">
         <v>41904</v>
@@ -758,37 +990,37 @@
       <c r="J9">
         <v>5</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>2:5;7:8</v>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>简单-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>easy</v>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" t="str">
-        <v>17,20</v>
-      </c>
-      <c r="F10" t="str">
-        <v>0.12,0.24</v>
-      </c>
-      <c r="G10" t="str">
-        <v>0.00,0.20</v>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
       </c>
       <c r="H10">
         <v>42017</v>
@@ -799,37 +1031,37 @@
       <c r="J10">
         <v>7</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>3:6;8:10</v>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>困难-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>hard</v>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
       </c>
       <c r="D11">
         <v>6</v>
       </c>
-      <c r="E11" t="str">
-        <v>20,25</v>
-      </c>
-      <c r="F11" t="str">
-        <v>0.12,0.24</v>
-      </c>
-      <c r="G11" t="str">
-        <v>0.06,0.32</v>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
       </c>
       <c r="H11">
         <v>42130</v>
@@ -840,37 +1072,37 @@
       <c r="J11">
         <v>8</v>
       </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>2:6;7:8;12:12</v>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
+      <c r="K11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>简单-11</v>
-      </c>
-      <c r="C12" t="str">
-        <v>easy</v>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="str">
-        <v>17,21</v>
-      </c>
-      <c r="F12" t="str">
-        <v>0.1,0.28</v>
-      </c>
-      <c r="G12" t="str">
-        <v>0.02,0.24</v>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
       </c>
       <c r="H12">
         <v>42243</v>
@@ -881,37 +1113,37 @@
       <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
+      <c r="K12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
       </c>
       <c r="M12">
         <v>9</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>简单-12</v>
-      </c>
-      <c r="C13" t="str">
-        <v>easy</v>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
-      <c r="E13" t="str">
-        <v>18,22</v>
-      </c>
-      <c r="F13" t="str">
-        <v>0.1,0.28</v>
-      </c>
-      <c r="G13" t="str">
-        <v>0.02,0.24</v>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
       </c>
       <c r="H13">
         <v>42356</v>
@@ -922,37 +1154,37 @@
       <c r="J13">
         <v>7</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
+      <c r="K13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>简单-13</v>
-      </c>
-      <c r="C14" t="str">
-        <v>easy</v>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
-      <c r="E14" t="str">
-        <v>18,22</v>
-      </c>
-      <c r="F14" t="str">
-        <v>0.1,0.28</v>
-      </c>
-      <c r="G14" t="str">
-        <v>0.02,0.24</v>
+      <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
       </c>
       <c r="H14">
         <v>42469</v>
@@ -963,37 +1195,37 @@
       <c r="J14">
         <v>8</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" t="s">
+        <v>18</v>
       </c>
       <c r="M14">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>简单-14</v>
-      </c>
-      <c r="C15" t="str">
-        <v>easy</v>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15" t="str">
-        <v>19,23</v>
-      </c>
-      <c r="F15" t="str">
-        <v>0.1,0.28</v>
-      </c>
-      <c r="G15" t="str">
-        <v>0.02,0.24</v>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
       </c>
       <c r="H15">
         <v>42582</v>
@@ -1004,37 +1236,37 @@
       <c r="J15">
         <v>11</v>
       </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v>2,8</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="K15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>中等-15</v>
-      </c>
-      <c r="C16" t="str">
-        <v>medium</v>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
       </c>
       <c r="D16">
         <v>7</v>
       </c>
-      <c r="E16" t="str">
-        <v>20,25</v>
-      </c>
-      <c r="F16" t="str">
-        <v>0.1,0.28</v>
-      </c>
-      <c r="G16" t="str">
-        <v>0.04,0.28</v>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
       </c>
       <c r="H16">
         <v>42695</v>
@@ -1045,37 +1277,37 @@
       <c r="J16">
         <v>10</v>
       </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v>2,6,10</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="K16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>简单-16</v>
-      </c>
-      <c r="C17" t="str">
-        <v>easy</v>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
-      <c r="E17" t="str">
-        <v>20,26</v>
-      </c>
-      <c r="F17" t="str">
-        <v>0.07,0.32</v>
-      </c>
-      <c r="G17" t="str">
-        <v>0.02,0.24</v>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
       </c>
       <c r="H17">
         <v>42808</v>
@@ -1084,39 +1316,39 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>13</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>6:6</v>
+        <v>12</v>
+      </c>
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" t="s">
+        <v>62</v>
       </c>
       <c r="M17">
         <v>3</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>简单-17</v>
-      </c>
-      <c r="C18" t="str">
-        <v>easy</v>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
-      <c r="E18" t="str">
-        <v>20,26</v>
-      </c>
-      <c r="F18" t="str">
-        <v>0.07,0.32</v>
-      </c>
-      <c r="G18" t="str">
-        <v>0.02,0.24</v>
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
       </c>
       <c r="H18">
         <v>42921</v>
@@ -1125,39 +1357,39 @@
         <v>2</v>
       </c>
       <c r="J18">
-        <v>11</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>6:10;15:6</v>
+        <v>10</v>
+      </c>
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" t="s">
+        <v>64</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>简单-18</v>
-      </c>
-      <c r="C19" t="str">
-        <v>easy</v>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
-      <c r="E19" t="str">
-        <v>21,28</v>
-      </c>
-      <c r="F19" t="str">
-        <v>0.07,0.32</v>
-      </c>
-      <c r="G19" t="str">
-        <v>0.02,0.24</v>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
       </c>
       <c r="H19">
         <v>43034</v>
@@ -1166,39 +1398,39 @@
         <v>3</v>
       </c>
       <c r="J19">
-        <v>11</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v>6:14;18:6</v>
-      </c>
-      <c r="M19" t="str">
-        <v>3,9</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>10</v>
+      </c>
+      <c r="K19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>简单-19</v>
-      </c>
-      <c r="C20" t="str">
-        <v>easy</v>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
-      <c r="E20" t="str">
-        <v>21,28</v>
-      </c>
-      <c r="F20" t="str">
-        <v>0.07,0.32</v>
-      </c>
-      <c r="G20" t="str">
-        <v>0.02,0.24</v>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" t="s">
+        <v>50</v>
       </c>
       <c r="H20">
         <v>43147</v>
@@ -1209,37 +1441,37 @@
       <c r="J20">
         <v>13</v>
       </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v>5:8;12:10;18:18</v>
-      </c>
-      <c r="M20" t="str">
-        <v>2,8</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="K20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>困难-20</v>
-      </c>
-      <c r="C21" t="str">
-        <v>hard</v>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
-      <c r="E21" t="str">
-        <v>30,35</v>
-      </c>
-      <c r="F21" t="str">
-        <v>0.07,0.32</v>
-      </c>
-      <c r="G21" t="str">
-        <v>0.06,0.32</v>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" t="s">
+        <v>45</v>
       </c>
       <c r="H21">
         <v>43260</v>
@@ -1250,19 +1482,21 @@
       <c r="J21">
         <v>15</v>
       </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v>7:8;15:12;23:14</v>
-      </c>
-      <c r="M21" t="str">
-        <v>3,8,13</v>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M21"/>
+    <ignoredError sqref="A1:M16 A21:M21 A17:I17 K17:M17 A18:I18 K18:M18 A19:I19 K19:M19 A20:I20 K20:M20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/excel/Levels.xlsx
+++ b/src/excel/Levels.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengbotao/fruit/src/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78567EF-63CF-244A-9F7C-88C87D50CC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F34CAF-F7FC-B441-892A-EC2EE7C64192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25200" yWindow="-24160" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -703,8 +703,8 @@
       <c r="J2">
         <v>3</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
+      <c r="K2">
+        <v>6</v>
       </c>
       <c r="L2" t="s">
         <v>18</v>
@@ -744,8 +744,8 @@
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3" t="s">
-        <v>18</v>
+      <c r="K3">
+        <v>6</v>
       </c>
       <c r="L3" t="s">
         <v>18</v>
@@ -785,8 +785,8 @@
       <c r="J4">
         <v>3</v>
       </c>
-      <c r="K4" t="s">
-        <v>18</v>
+      <c r="K4">
+        <v>5</v>
       </c>
       <c r="L4" t="s">
         <v>18</v>
@@ -826,8 +826,8 @@
       <c r="J5">
         <v>3</v>
       </c>
-      <c r="K5" t="s">
-        <v>18</v>
+      <c r="K5">
+        <v>5</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -867,8 +867,8 @@
       <c r="J6">
         <v>4</v>
       </c>
-      <c r="K6" t="s">
-        <v>18</v>
+      <c r="K6">
+        <v>5</v>
       </c>
       <c r="L6" t="s">
         <v>18</v>
@@ -908,8 +908,8 @@
       <c r="J7">
         <v>4</v>
       </c>
-      <c r="K7" t="s">
-        <v>18</v>
+      <c r="K7">
+        <v>6</v>
       </c>
       <c r="L7" t="s">
         <v>32</v>
@@ -949,8 +949,8 @@
       <c r="J8">
         <v>7</v>
       </c>
-      <c r="K8" t="s">
-        <v>18</v>
+      <c r="K8">
+        <v>9</v>
       </c>
       <c r="L8" t="s">
         <v>35</v>
@@ -990,8 +990,8 @@
       <c r="J9">
         <v>5</v>
       </c>
-      <c r="K9" t="s">
-        <v>18</v>
+      <c r="K9">
+        <v>7</v>
       </c>
       <c r="L9" t="s">
         <v>38</v>
@@ -1031,8 +1031,8 @@
       <c r="J10">
         <v>7</v>
       </c>
-      <c r="K10" t="s">
-        <v>18</v>
+      <c r="K10">
+        <v>9</v>
       </c>
       <c r="L10" t="s">
         <v>41</v>
@@ -1072,8 +1072,8 @@
       <c r="J11">
         <v>8</v>
       </c>
-      <c r="K11" t="s">
-        <v>18</v>
+      <c r="K11">
+        <v>9</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
@@ -1113,8 +1113,8 @@
       <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12" t="s">
-        <v>18</v>
+      <c r="K12">
+        <v>8</v>
       </c>
       <c r="L12" t="s">
         <v>18</v>
@@ -1154,8 +1154,8 @@
       <c r="J13">
         <v>7</v>
       </c>
-      <c r="K13" t="s">
-        <v>18</v>
+      <c r="K13">
+        <v>9</v>
       </c>
       <c r="L13" t="s">
         <v>18</v>
@@ -1195,8 +1195,8 @@
       <c r="J14">
         <v>8</v>
       </c>
-      <c r="K14" t="s">
-        <v>18</v>
+      <c r="K14">
+        <v>10</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -1236,8 +1236,8 @@
       <c r="J15">
         <v>11</v>
       </c>
-      <c r="K15" t="s">
-        <v>18</v>
+      <c r="K15">
+        <v>12</v>
       </c>
       <c r="L15" t="s">
         <v>18</v>
@@ -1277,8 +1277,8 @@
       <c r="J16">
         <v>10</v>
       </c>
-      <c r="K16" t="s">
-        <v>18</v>
+      <c r="K16">
+        <v>11</v>
       </c>
       <c r="L16" t="s">
         <v>18</v>
@@ -1318,8 +1318,8 @@
       <c r="J17">
         <v>12</v>
       </c>
-      <c r="K17" t="s">
-        <v>18</v>
+      <c r="K17">
+        <v>14</v>
       </c>
       <c r="L17" t="s">
         <v>62</v>
@@ -1359,8 +1359,8 @@
       <c r="J18">
         <v>10</v>
       </c>
-      <c r="K18" t="s">
-        <v>18</v>
+      <c r="K18">
+        <v>12</v>
       </c>
       <c r="L18" t="s">
         <v>64</v>
@@ -1400,8 +1400,8 @@
       <c r="J19">
         <v>10</v>
       </c>
-      <c r="K19" t="s">
-        <v>18</v>
+      <c r="K19">
+        <v>11</v>
       </c>
       <c r="L19" t="s">
         <v>67</v>
@@ -1441,8 +1441,8 @@
       <c r="J20">
         <v>13</v>
       </c>
-      <c r="K20" t="s">
-        <v>18</v>
+      <c r="K20">
+        <v>14</v>
       </c>
       <c r="L20" t="s">
         <v>70</v>
@@ -1482,8 +1482,8 @@
       <c r="J21">
         <v>15</v>
       </c>
-      <c r="K21" t="s">
-        <v>18</v>
+      <c r="K21">
+        <v>15</v>
       </c>
       <c r="L21" t="s">
         <v>73</v>
@@ -1496,7 +1496,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M16 A21:M21 A17:I17 K17:M17 A18:I18 K18:M18 A19:I19 K19:M19 A20:I20 K20:M20" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M1 A21:J21 A17:I17 L17:M17 A18:I18 L18:M18 A19:I19 L19:M19 A20:I20 L20:M20 A16:J16 A2:J2 L2:M2 A3:J3 L3:M3 A4:J4 L4:M4 A5:J5 L5:M5 A6:J6 L6:M6 A7:J7 L7:M7 A8:J8 L8:M8 A9:J9 L9:M9 A10:J10 L10:M10 A11:J11 L11:M11 A12:J12 L12:M12 A13:J13 L13:M13 A14:J14 L14:M14 A15:J15 L15:M15 L16:M16 L21:M21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>